--- a/data/trans_orig/IP31KM09_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM09_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108357</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83465</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>117948</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>104630</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98406</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108886</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119550</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131141</t>
+          <t>112972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>224180</t>
+          <t>217641</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189366</t>
+          <t>194117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236736</t>
+          <t>227794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14539</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4948</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39431</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9621</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15845</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26886</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>219773</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>212441</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>224712</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>179112</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>173923</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>181977</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>234919</t>
+          <t>174206</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225572</t>
+          <t>170091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239507</t>
+          <t>177148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>393978</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404416</t>
+          <t>384711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>420520</t>
+          <t>400176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11468</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6529</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18800</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29218</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>156218</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>148476</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>160736</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>172997</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>165061</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>179599</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>172360</t>
+          <t>139336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163727</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177084</t>
+          <t>145012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>345358</t>
+          <t>295554</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>334550</t>
+          <t>284699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353398</t>
+          <t>302998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18046</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15252</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8650</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23188</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36789</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>152510</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>145143</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157774</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>150638</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>142883</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>155741</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>150321</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155024</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168400</t>
+          <t>155182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>313118</t>
+          <t>302831</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>302705</t>
+          <t>292715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321209</t>
+          <t>310489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>636857</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>607353</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>650829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>844</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>607377</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>594531</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>618007</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>643635</t>
+          <t>561227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>704732</t>
+          <t>582761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1256992</t>
+          <t>1181271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1314187</t>
+          <t>1226927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35995</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>79471</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>35127</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58603</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83680</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
